--- a/Family_Office_Portfolio_Allocator.xlsx
+++ b/Family_Office_Portfolio_Allocator.xlsx
@@ -3196,6 +3196,7 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
@@ -3218,6 +3219,11 @@
           <t>Target %</t>
         </is>
       </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Remaining Gap to Target (KWD)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
@@ -3237,6 +3243,10 @@
         <f>D6</f>
         <v/>
       </c>
+      <c r="F22" s="21">
+        <f>MAX(0,E22*New_Total-C22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
@@ -3256,6 +3266,10 @@
         <f>D7</f>
         <v/>
       </c>
+      <c r="F23" s="21">
+        <f>MAX(0,E23*New_Total-C23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
@@ -3275,6 +3289,10 @@
         <f>D8</f>
         <v/>
       </c>
+      <c r="F24" s="21">
+        <f>MAX(0,E24*New_Total-C24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
@@ -3294,6 +3312,10 @@
         <f>D9</f>
         <v/>
       </c>
+      <c r="F25" s="21">
+        <f>MAX(0,E25*New_Total-C25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="12" t="inlineStr">
@@ -3311,15 +3333,19 @@
       </c>
       <c r="E26" s="13">
         <f>SUM(E22:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="23">
+        <f>SUM(F22:F25)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3453,7 +3479,7 @@
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>IF(AND(ABS(G6)&gt;Tol_Band,ABS(F6)&gt;Min_Action),IF(F6&gt;0,"Increase","Reduce"),"Hold")</f>
+        <f>IF(ABS(G6)&lt;=Tol_Band,"Hold",IF(F6&gt;0,"Increase","Reduce"))</f>
         <v/>
       </c>
     </row>
@@ -3484,7 +3510,7 @@
         <v/>
       </c>
       <c r="H7" s="32">
-        <f>IF(AND(ABS(G7)&gt;Tol_Band,ABS(F7)&gt;Min_Action),IF(F7&gt;0,"Increase","Reduce"),"Hold")</f>
+        <f>IF(ABS(G7)&lt;=Tol_Band,"Hold",IF(F7&gt;0,"Increase","Reduce"))</f>
         <v/>
       </c>
     </row>
@@ -3515,7 +3541,7 @@
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>IF(AND(ABS(G8)&gt;Tol_Band,ABS(F8)&gt;Min_Action),IF(F8&gt;0,"Increase","Reduce"),"Hold")</f>
+        <f>IF(ABS(G8)&lt;=Tol_Band,"Hold",IF(F8&gt;0,"Increase","Reduce"))</f>
         <v/>
       </c>
     </row>
@@ -3546,7 +3572,7 @@
         <v/>
       </c>
       <c r="H9" s="32">
-        <f>IF(AND(ABS(G9)&gt;Tol_Band,ABS(F9)&gt;Min_Action),IF(F9&gt;0,"Increase","Reduce"),"Hold")</f>
+        <f>IF(ABS(G9)&lt;=Tol_Band,"Hold",IF(F9&gt;0,"Increase","Reduce"))</f>
         <v/>
       </c>
     </row>
@@ -3723,7 +3749,7 @@
         </is>
       </c>
       <c r="C29" s="21">
-        <f>IF(H6&lt;&gt;"Hold",E6,C6)</f>
+        <f>IF(COUNTIF($H$6:$H$9,"Hold")=4,C6,E6)</f>
         <v/>
       </c>
       <c r="D29" s="24">
@@ -3742,7 +3768,7 @@
         </is>
       </c>
       <c r="C30" s="21">
-        <f>IF(H7&lt;&gt;"Hold",E7,C7)</f>
+        <f>IF(COUNTIF($H$6:$H$9,"Hold")=4,C7,E7)</f>
         <v/>
       </c>
       <c r="D30" s="24">
@@ -3761,7 +3787,7 @@
         </is>
       </c>
       <c r="C31" s="21">
-        <f>IF(H8&lt;&gt;"Hold",E8,C8)</f>
+        <f>IF(COUNTIF($H$6:$H$9,"Hold")=4,C8,E8)</f>
         <v/>
       </c>
       <c r="D31" s="24">
@@ -3780,7 +3806,7 @@
         </is>
       </c>
       <c r="C32" s="21">
-        <f>IF(H9&lt;&gt;"Hold",E9,C9)</f>
+        <f>IF(COUNTIF($H$6:$H$9,"Hold")=4,C9,E9)</f>
         <v/>
       </c>
       <c r="D32" s="24">
@@ -3814,7 +3840,7 @@
     <row r="34">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Assumes recommended moves are executed: classes flagged for action are moved to their target weight; classes within tolerance are held and may remain slightly off target. Any net cash difference is settled from the cash account.</t>
+          <t>A rebalance moves capital from overweight to underweight classes; the portfolio total is unchanged and no new capital is added. When any class breaches the tolerance band, the portfolio is returned to its strategic target weights (shown above); the 'Action' column flags which classes have drifted.</t>
         </is>
       </c>
     </row>
